--- a/data_out/country_spreadsheets/Czechia.xlsx
+++ b/data_out/country_spreadsheets/Czechia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>51.71</v>
       </c>
+      <c r="X2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>131.59</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>82.88</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>203.57</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>359.08</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>201.05</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>27.64</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>51.71</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>76.28</v>
       </c>
+      <c r="X3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>23.94</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>113.29</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>75.05</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>32.77</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>203.84</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>312.59</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>155.97</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>49.71</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>76.28</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>66.22</v>
       </c>
+      <c r="X4" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>60.29</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>169.34</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>87.78</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>171.96</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>90.84</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>66.22</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>76.76000000000001</v>
       </c>
+      <c r="X5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>37.21</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>56.77</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>143.9</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>193.17</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>153.45</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>74.06999999999999</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>81.72</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>76.76000000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>82.97</v>
       </c>
+      <c r="X6" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>77.98</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>188.61</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>255.04</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>137.8</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>108.23</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>82.89</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>82.97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>75.73</v>
       </c>
+      <c r="X7" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>39.67</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>37.79</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>196.74</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>245.29</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>168.26</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>101.15</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>87.11</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>75.73</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>48.36</v>
       </c>
+      <c r="X8" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>33.44</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>58.14</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>128.29</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>200.4</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>256.69</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>125.04</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>41</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>48.36</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1160,6 +1602,57 @@
       <c r="W9" t="n">
         <v>57.02</v>
       </c>
+      <c r="X9" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>34.61</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>80.93000000000001</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>180.64</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>90.52</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>51.14</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>182.66</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>156.38</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>57.02</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1237,6 +1730,57 @@
       <c r="W10" t="n">
         <v>93.53</v>
       </c>
+      <c r="X10" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>46.51</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>149.06</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>135.9</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>125.26</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>237.35</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>196.31</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>100.41</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>54.12</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>93.53</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1314,6 +1858,57 @@
       <c r="W11" t="n">
         <v>105.93</v>
       </c>
+      <c r="X11" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>152.23</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>151.75</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>244.79</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>212.21</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>97.13</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>87.89</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>70.98</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>105.93</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1391,6 +1986,57 @@
       <c r="W12" t="n">
         <v>52.03</v>
       </c>
+      <c r="X12" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>229.39</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>134.79</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>198.43</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>200.44</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>165.53</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>40.02</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>97.95999999999999</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>60.74</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>52.03</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1468,6 +2114,57 @@
       <c r="W13" t="n">
         <v>83.18000000000001</v>
       </c>
+      <c r="X13" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>123.39</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>78.37</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>205.87</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>193.99</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>185</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>58.97</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>165.83</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>74.01000000000001</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>83.18000000000001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1545,6 +2242,57 @@
       <c r="W14" t="n">
         <v>82.42</v>
       </c>
+      <c r="X14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>33.26</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>191.63</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>26.83</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>91.73</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>188.28</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>186.29</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>174.69</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>247.85</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>175.73</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>35.09</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>239.03</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>59.49</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>82.42</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1620,6 +2368,57 @@
         <v>23.24</v>
       </c>
       <c r="W15" t="n">
+        <v>104.43</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>90.47</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>163.46</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>182.07</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>39.86</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>189.08</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>180.84</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>61.83</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>133.23</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>78.05</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="AN15" t="n">
         <v>104.43</v>
       </c>
     </row>
